--- a/sample test data.xlsx
+++ b/sample test data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\crm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0EAF3C3-C414-4620-815F-00233425FFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D78035-CCCD-41BD-9572-1F6D259188AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6996" yWindow="1560" windowWidth="12756" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7344" yWindow="1908" windowWidth="12756" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -790,9 +790,7 @@
       <c r="D7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="8">
-        <v>6000000000</v>
-      </c>
+      <c r="E7" s="8"/>
       <c r="F7" s="8" t="s">
         <v>37</v>
       </c>
